--- a/output/pdf_financials_xlsx/EQTY.xlsx
+++ b/output/pdf_financials_xlsx/EQTY.xlsx
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>1.655612</v>
+        <v>0.219328</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1.086566</v>
+        <v>0</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-1.643701</v>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.7181419999999999</v>
+        <v>-0.7181419999999999</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.543283</v>
+        <v>-0.543283</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-1.633701</v>
@@ -1871,10 +1871,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.7181419999999999</v>
+        <v>-0.7181419999999999</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.543283</v>
+        <v>-0.543283</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-1.633701</v>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-35.9071</v>
+        <v>35.9071</v>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
@@ -2179,10 +2179,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>1.655612</v>
+        <v>0.219328</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1.086566</v>
+        <v>0</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-1.643701</v>
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>1.655612</v>
+        <v>0.219328</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1.086566</v>
+        <v>0</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-1.627078</v>
@@ -2469,10 +2469,12 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>56.6237741693102</v>
-      </c>
-      <c r="C31" s="3" t="n">
-        <v>50</v>
+        <v>427.4283265246571</v>
+      </c>
+      <c r="C31" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0.6083831548438554</v>
@@ -6154,49 +6156,49 @@
         <v>2.025975</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.649798</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.426245</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.602732</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.602732</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.602732</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.602732</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.671332</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.818806</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.918312</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>3.220771</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>4.322467</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>4.927552</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>5.415227</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>5.461441</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>6.073837</v>
       </c>
     </row>
     <row r="93">
@@ -10463,7 +10465,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -12979,7 +12985,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -13789,7 +13799,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -15102,7 +15116,11 @@
           <t>Reserves (Note 8(e)) 2,818,806</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -16898,7 +16916,11 @@
           <t>Reserves (Note 8(e))</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -18258,7 +18280,11 @@
           <t>Reserves (Note 6(e))</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
@@ -18646,7 +18672,11 @@
           <t>Reserves (Note 6 (e))</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
@@ -19715,7 +19745,11 @@
           <t>Reserves (Note 8 (e))</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -46925,10 +46959,10 @@
         </is>
       </c>
       <c r="E384" s="5" t="n">
-        <v>0.7181419999999999</v>
+        <v>-0.7181419999999999</v>
       </c>
       <c r="F384" s="5" t="n">
-        <v>0.543283</v>
+        <v>-0.543283</v>
       </c>
       <c r="G384" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/EQTY.xlsx
+++ b/output/pdf_financials_xlsx/EQTY.xlsx
@@ -1093,16 +1093,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.004984</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-9.899999999999999e-05</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000355</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000862</v>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
@@ -2179,16 +2179,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.219328</v>
+        <v>0.224312</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0</v>
+        <v>9.899999999999999e-05</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.643701</v>
+        <v>-1.643346</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.124639</v>
+        <v>-1.123777</v>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
@@ -2311,16 +2311,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.219328</v>
+        <v>0.224312</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0</v>
+        <v>9.899999999999999e-05</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.627078</v>
+        <v>-1.626723</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.108823</v>
+        <v>-1.107961</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
@@ -2636,16 +2636,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.127367</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.346671</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.629453</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.150655</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0.153456</v>
@@ -2657,22 +2657,22 @@
         <v>0.021689</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.008241</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.437239</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0.437239</v>
+        <v>0.58439</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.035583</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.790432</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.787472</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>0.49752</v>
@@ -2752,16 +2752,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.127367</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.346671</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.629453</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.150655</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>0.153456</v>
@@ -2773,22 +2773,22 @@
         <v>0.021689</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.008241</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.366675</v>
+        <v>0.803914</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.460738</v>
+        <v>0.607889</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.035583</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.790432</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.787472</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>0.49752</v>
@@ -3451,13 +3451,13 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.510053</v>
+        <v>0.163382</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.821689</v>
+        <v>0.192236</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.225393</v>
+        <v>0.074738</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0.027785</v>
@@ -3469,22 +3469,22 @@
         <v>0.004524</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.015859</v>
+        <v>0.007618</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.08235000000000001</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.216229</v>
+        <v>0.069078</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.115211</v>
+        <v>0.079628</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.979281</v>
+        <v>0.188849</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.942217</v>
+        <v>0.154745</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>0.081869</v>
@@ -10914,7 +10914,11 @@
           <t>Reclamation deposits 4, 6</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -11217,7 +11221,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11504,7 +11508,11 @@
           <t>Reclamation deposits 4</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -12385,7 +12393,11 @@
           <t>Reclamation deposits 3</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -13193,7 +13205,11 @@
           <t>Reclamation deposits 5,8</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -14302,7 +14318,11 @@
           <t>Reclamation deposits (Note 5) 82,500</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -15924,7 +15944,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -16221,7 +16241,11 @@
           <t>Reclamation deposits (Note 5)</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -17710,7 +17734,11 @@
           <t>Reclamation deposits (Note 3)</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -19848,7 +19876,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
@@ -31699,7 +31727,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -32796,7 +32828,11 @@
           <t>Increase in reclamation deposits</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr">
         <is>
           <t>-</t>
@@ -44646,7 +44682,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E361" s="5" t="n">
